--- a/data/trans_dic/P20D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,5</t>
+          <t>0,0; 49,31</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,57; 92,23</t>
+          <t>41,95; 92,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,7; 89,06</t>
+          <t>26,29; 90,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,83; 88,87</t>
+          <t>45,23; 89,71</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,27; 100,0</t>
+          <t>58,53; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,66</t>
+          <t>0,0; 46,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,84; 77,43</t>
+          <t>38,99; 77,45</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,55; 100,0</t>
+          <t>39,44; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,0; 88,2</t>
+          <t>13,7; 85,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,78; 82,92</t>
+          <t>38,44; 84,21</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,02; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,3; 90,78</t>
+          <t>24,32; 90,68</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,84; 92,5</t>
+          <t>37,33; 92,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,68; 91,29</t>
+          <t>14,7; 91,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,32; 83,3</t>
+          <t>40,77; 85,76</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,12; 87,79</t>
+          <t>22,66; 88,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,0; 53,25</t>
+          <t>17,8; 54,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,39; 58,48</t>
+          <t>25,08; 61,62</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,76; 97,77</t>
+          <t>39,9; 97,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,14</t>
+          <t>0,0; 70,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,34; 80,04</t>
+          <t>34,08; 81,22</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58,54; 80,67</t>
+          <t>58,73; 80,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,26; 53,16</t>
+          <t>25,77; 51,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47,82; 64,54</t>
+          <t>47,09; 65,0</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1407</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2345</t>
+          <t>0; 2541</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5560; 14021</t>
+          <t>6378; 14011</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1565; 5424</t>
+          <t>1601; 5494</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9972; 18923</t>
+          <t>9632; 19102</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6225; 11062</t>
+          <t>6475; 11062</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3315</t>
+          <t>0; 3149</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7121; 13841</t>
+          <t>6970; 13846</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3513; 8663</t>
+          <t>3416; 8663</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1241; 9120</t>
+          <t>1417; 8817</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6990; 15758</t>
+          <t>7306; 16004</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>662; 2283</t>
+          <t>0; 2283</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1000; 3098</t>
+          <t>830; 3095</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2416; 5753</t>
+          <t>2322; 5725</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>482; 2998</t>
+          <t>483; 3016</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3737; 7917</t>
+          <t>3875; 8151</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1716; 7877</t>
+          <t>2033; 7898</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2581; 8084</t>
+          <t>2702; 8246</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6375; 14126</t>
+          <t>6058; 14884</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3090; 7235</t>
+          <t>2953; 7233</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3075</t>
+          <t>0; 3033</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3909; 9382</t>
+          <t>3994; 9520</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>36456; 50242</t>
+          <t>36577; 50411</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14084; 26495</t>
+          <t>12843; 25658</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53611; 72362</t>
+          <t>52796; 72878</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Provincia-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,97</t>
+          <t>0,0; 69,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,31</t>
+          <t>0,0; 57,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,95; 92,16</t>
+          <t>47,1; 93,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,29; 90,21</t>
+          <t>24,25; 88,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,23; 89,71</t>
+          <t>46,37; 87,17</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,53; 100,0</t>
+          <t>57,69; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,23</t>
+          <t>0,0; 48,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,99; 77,45</t>
+          <t>39,43; 76,57</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>63,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,44; 100,0</t>
+          <t>48,02; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 85,27</t>
+          <t>13,95; 85,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,44; 84,21</t>
+          <t>38,55; 83,33</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,09%</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,32; 90,68</t>
+          <t>19,56; 90,29</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,79%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,33; 92,04</t>
+          <t>34,89; 92,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,7; 91,85</t>
+          <t>13,36; 92,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,77; 85,76</t>
+          <t>39,83; 84,84</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,66; 88,02</t>
+          <t>26,12; 87,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,8; 54,32</t>
+          <t>24,61; 59,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,08; 61,62</t>
+          <t>30,63; 62,11</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,9; 97,74</t>
+          <t>34,07; 91,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,19</t>
+          <t>0,0; 75,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34,08; 81,22</t>
+          <t>32,41; 77,25</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58,73; 80,95</t>
+          <t>61,02; 82,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25,77; 51,48</t>
+          <t>29,01; 52,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47,09; 65,0</t>
+          <t>49,15; 64,92</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>1031</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>0; 2076</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2541</t>
+          <t>0; 2948</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>16419</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6378; 14011</t>
+          <t>7873; 15556</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1601; 5494</t>
+          <t>1590; 5818</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9632; 19102</t>
+          <t>10792; 20286</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10470</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6475; 11062</t>
+          <t>6176; 10706</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3149</t>
+          <t>0; 3347</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6970; 13846</t>
+          <t>6965; 13525</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>14121</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3416; 8663</t>
+          <t>5164; 10754</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1417; 8817</t>
+          <t>1599; 9770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7306; 16004</t>
+          <t>8565; 18514</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>384</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2335</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2283</t>
+          <t>0; 2448</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1130</t>
+          <t>0; 1195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>830; 3095</t>
+          <t>713; 3289</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6101</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2322; 5725</t>
+          <t>2129; 5624</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>483; 3016</t>
+          <t>442; 3048</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3875; 8151</t>
+          <t>3750; 7988</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>14417</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2033; 7898</t>
+          <t>2792; 9323</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2702; 8246</t>
+          <t>4915; 11965</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6058; 14884</t>
+          <t>9391; 19047</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>7406</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2953; 7233</t>
+          <t>2944; 7928</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3033</t>
+          <t>0; 3631</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3994; 9520</t>
+          <t>4368; 10412</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>72300</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>36577; 50411</t>
+          <t>41618; 56405</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12843; 25658</t>
+          <t>16616; 30142</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52796; 72878</t>
+          <t>61674; 81467</t>
         </is>
       </c>
     </row>
